--- a/FINAL450.xlsx
+++ b/FINAL450.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\DO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\DSA 450\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF75014-3027-4916-95CC-CE2D12503FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC81DB20-A2FE-4B74-A92F-514BA9D7ED80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
   </bookViews>
@@ -1483,12 +1483,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1504,7 +1510,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1523,6 +1529,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1862,7 +1871,7 @@
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -1873,7 +1882,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1884,7 +1893,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1895,7 +1904,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1906,7 +1915,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1917,7 +1926,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
